--- a/Plannings 2026 S27.xlsx
+++ b/Plannings 2026 S27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43903BD4-F6FF-48EB-A0B3-1489F1118A0B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="121">
   <si>
     <t>Planning des salariés du 29/06/2026 au 05/07/2026</t>
   </si>
@@ -379,6 +379,12 @@
   </si>
   <si>
     <t>C. PADEL // LEAGUES</t>
+  </si>
+  <si>
+    <t>18:00/00:30+</t>
+  </si>
+  <si>
+    <t>18:30/01:00+</t>
   </si>
 </sst>
 </file>
@@ -767,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -936,6 +942,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4411,8 +4423,8 @@
       <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>55</v>
+      <c r="C27" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>56</v>
@@ -4581,8 +4593,8 @@
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23"/>
       <c r="B39" s="24"/>
-      <c r="C39" s="24" t="s">
-        <v>70</v>
+      <c r="C39" s="58" t="s">
+        <v>120</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24" t="s">
@@ -5749,13 +5761,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A6ACA25-883F-46DD-8FAC-0088F0126280}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC7D462-6616-4EBC-99F4-A6C0B3B6308F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69510268-CC1B-4632-A4CB-6AE030FC320A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29687674-ECD2-46B3-93B0-F504DA9E2663}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCDBF4C9-CA0B-43D3-A1A0-B0B5BDEF8381}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A18A57DC-3390-445A-B912-A214DBB6007F}"/>
 </file>
--- a/Plannings 2026 S27.xlsx
+++ b/Plannings 2026 S27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43903BD4-F6FF-48EB-A0B3-1489F1118A0B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="119">
   <si>
     <t>Planning des salariés du 29/06/2026 au 05/07/2026</t>
   </si>
@@ -379,12 +379,6 @@
   </si>
   <si>
     <t>C. PADEL // LEAGUES</t>
-  </si>
-  <si>
-    <t>18:00/00:30+</t>
-  </si>
-  <si>
-    <t>18:30/01:00+</t>
   </si>
 </sst>
 </file>
@@ -773,7 +767,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -942,12 +936,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4423,8 +4411,8 @@
       <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="57" t="s">
-        <v>119</v>
+      <c r="C27" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>56</v>
@@ -4593,8 +4581,8 @@
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23"/>
       <c r="B39" s="24"/>
-      <c r="C39" s="58" t="s">
-        <v>120</v>
+      <c r="C39" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24" t="s">
@@ -5761,13 +5749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC7D462-6616-4EBC-99F4-A6C0B3B6308F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A6ACA25-883F-46DD-8FAC-0088F0126280}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29687674-ECD2-46B3-93B0-F504DA9E2663}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69510268-CC1B-4632-A4CB-6AE030FC320A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A18A57DC-3390-445A-B912-A214DBB6007F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCDBF4C9-CA0B-43D3-A1A0-B0B5BDEF8381}"/>
 </file>
--- a/Plannings 2026 S27.xlsx
+++ b/Plannings 2026 S27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43903BD4-F6FF-48EB-A0B3-1489F1118A0B}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8622FDF1-36D1-43BB-88B8-BE01069C0AF7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="124">
   <si>
     <t>Planning des salariés du 29/06/2026 au 05/07/2026</t>
   </si>
@@ -381,10 +381,19 @@
     <t>C. PADEL // LEAGUES</t>
   </si>
   <si>
-    <t>18:00/00:30+</t>
-  </si>
-  <si>
     <t>18:30/01:00+</t>
+  </si>
+  <si>
+    <t>18:00/19:00</t>
+  </si>
+  <si>
+    <t>EV-LO</t>
+  </si>
+  <si>
+    <t>19:00/23:00</t>
+  </si>
+  <si>
+    <t>23:00/00:30+</t>
   </si>
 </sst>
 </file>
@@ -773,7 +782,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -949,6 +958,12 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3605,6 +3620,138 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15BE6346-770A-4827-976C-2BE0919065FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="6867525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28838D5F-AC93-4BBB-B87B-CEC48C3B906C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="7248525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4796696F-9039-4729-AF11-3B924332FD4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="7629525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4403,7 +4550,7 @@
       <c r="B26" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="39" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="49" t="s">
@@ -4424,7 +4571,7 @@
         <v>55</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>56</v>
@@ -4441,7 +4588,9 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="28"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="C28" s="59" t="s">
+        <v>121</v>
+      </c>
       <c r="D28" s="32" t="s">
         <v>54</v>
       </c>
@@ -4455,7 +4604,9 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="C29" s="60" t="s">
+        <v>122</v>
+      </c>
       <c r="D29" s="31" t="s">
         <v>58</v>
       </c>
@@ -4469,7 +4620,9 @@
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
+      <c r="C30" s="39" t="s">
+        <v>14</v>
+      </c>
       <c r="D30" s="52" t="s">
         <v>53</v>
       </c>
@@ -4481,7 +4634,9 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
+      <c r="C31" s="57" t="s">
+        <v>123</v>
+      </c>
       <c r="D31" s="50" t="s">
         <v>60</v>
       </c>
@@ -4493,7 +4648,7 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="28"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="C32" s="57"/>
       <c r="D32" s="2" t="s">
         <v>14</v>
       </c>
@@ -4505,7 +4660,7 @@
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23"/>
       <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
+      <c r="C33" s="57"/>
       <c r="D33" s="24" t="s">
         <v>61</v>
       </c>
@@ -4594,7 +4749,7 @@
       <c r="A39" s="23"/>
       <c r="B39" s="24"/>
       <c r="C39" s="58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24" t="s">
@@ -5761,13 +5916,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC7D462-6616-4EBC-99F4-A6C0B3B6308F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F903DBC4-089F-4C3C-B318-6D055EAA38B4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29687674-ECD2-46B3-93B0-F504DA9E2663}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F45498C-9A62-4276-91DA-5E62C1AFB4E9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A18A57DC-3390-445A-B912-A214DBB6007F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5961727-1632-4E8E-BB6E-991B1EDC4857}"/>
 </file>
--- a/Plannings 2026 S27.xlsx
+++ b/Plannings 2026 S27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8622FDF1-36D1-43BB-88B8-BE01069C0AF7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="119">
   <si>
     <t>Planning des salariés du 29/06/2026 au 05/07/2026</t>
   </si>
@@ -379,21 +379,6 @@
   </si>
   <si>
     <t>C. PADEL // LEAGUES</t>
-  </si>
-  <si>
-    <t>18:30/01:00+</t>
-  </si>
-  <si>
-    <t>18:00/19:00</t>
-  </si>
-  <si>
-    <t>EV-LO</t>
-  </si>
-  <si>
-    <t>19:00/23:00</t>
-  </si>
-  <si>
-    <t>23:00/00:30+</t>
   </si>
 </sst>
 </file>
@@ -782,7 +767,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -952,18 +937,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3620,138 +3593,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15BE6346-770A-4827-976C-2BE0919065FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="6867525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28838D5F-AC93-4BBB-B87B-CEC48C3B906C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="7248525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4796696F-9039-4729-AF11-3B924332FD4C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="7629525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4550,7 +4391,7 @@
       <c r="B26" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="21" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="49" t="s">
@@ -4570,8 +4411,8 @@
       <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="57" t="s">
-        <v>120</v>
+      <c r="C27" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>56</v>
@@ -4588,9 +4429,7 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="28"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="59" t="s">
-        <v>121</v>
-      </c>
+      <c r="C28" s="1"/>
       <c r="D28" s="32" t="s">
         <v>54</v>
       </c>
@@ -4604,9 +4443,7 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="60" t="s">
-        <v>122</v>
-      </c>
+      <c r="C29" s="1"/>
       <c r="D29" s="31" t="s">
         <v>58</v>
       </c>
@@ -4620,9 +4457,7 @@
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="39" t="s">
-        <v>14</v>
-      </c>
+      <c r="C30" s="1"/>
       <c r="D30" s="52" t="s">
         <v>53</v>
       </c>
@@ -4634,9 +4469,7 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="57" t="s">
-        <v>123</v>
-      </c>
+      <c r="C31" s="1"/>
       <c r="D31" s="50" t="s">
         <v>60</v>
       </c>
@@ -4648,7 +4481,7 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="28"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="57"/>
+      <c r="C32" s="1"/>
       <c r="D32" s="2" t="s">
         <v>14</v>
       </c>
@@ -4660,7 +4493,7 @@
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23"/>
       <c r="B33" s="24"/>
-      <c r="C33" s="57"/>
+      <c r="C33" s="24"/>
       <c r="D33" s="24" t="s">
         <v>61</v>
       </c>
@@ -4748,8 +4581,8 @@
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23"/>
       <c r="B39" s="24"/>
-      <c r="C39" s="58" t="s">
-        <v>119</v>
+      <c r="C39" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24" t="s">
@@ -5916,13 +5749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F903DBC4-089F-4C3C-B318-6D055EAA38B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A6ACA25-883F-46DD-8FAC-0088F0126280}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F45498C-9A62-4276-91DA-5E62C1AFB4E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69510268-CC1B-4632-A4CB-6AE030FC320A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5961727-1632-4E8E-BB6E-991B1EDC4857}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCDBF4C9-CA0B-43D3-A1A0-B0B5BDEF8381}"/>
 </file>
--- a/Plannings 2026 S27.xlsx
+++ b/Plannings 2026 S27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8622FDF1-36D1-43BB-88B8-BE01069C0AF7}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C34AB7D-5334-4298-96BE-5C6DE48BC88A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,9 +378,6 @@
     <t>JPO PADEL KIDS // ANNIV</t>
   </si>
   <si>
-    <t>C. PADEL // LEAGUES</t>
-  </si>
-  <si>
     <t>18:30/01:00+</t>
   </si>
   <si>
@@ -394,6 +391,9 @@
   </si>
   <si>
     <t>23:00/00:30+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      C. PADEL    //    LEAGUES     //      16eme FRANCE</t>
   </si>
 </sst>
 </file>
@@ -4168,7 +4168,7 @@
         <v>114</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D3" s="56" t="s">
         <v>115</v>
@@ -4571,7 +4571,7 @@
         <v>55</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>56</v>
@@ -4589,7 +4589,7 @@
       <c r="A28" s="28"/>
       <c r="B28" s="1"/>
       <c r="C28" s="59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D28" s="32" t="s">
         <v>54</v>
@@ -4605,7 +4605,7 @@
       <c r="A29" s="28"/>
       <c r="B29" s="1"/>
       <c r="C29" s="60" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D29" s="31" t="s">
         <v>58</v>
@@ -4635,7 +4635,7 @@
       <c r="A31" s="28"/>
       <c r="B31" s="1"/>
       <c r="C31" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D31" s="50" t="s">
         <v>60</v>
@@ -4749,7 +4749,7 @@
       <c r="A39" s="23"/>
       <c r="B39" s="24"/>
       <c r="C39" s="58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24" t="s">
@@ -5916,13 +5916,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F903DBC4-089F-4C3C-B318-6D055EAA38B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0E364D-2D39-4FA9-BB2A-721348C3EA28}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F45498C-9A62-4276-91DA-5E62C1AFB4E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC0ACA86-0276-4A26-B4FA-4A2B4920F358}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5961727-1632-4E8E-BB6E-991B1EDC4857}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8BB1F4E-294E-4892-B1AE-5BD18185F0D7}"/>
 </file>
--- a/Plannings 2026 S27.xlsx
+++ b/Plannings 2026 S27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C34AB7D-5334-4298-96BE-5C6DE48BC88A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9BD0506-81E3-457E-ABEF-F9CA295F4E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="119">
   <si>
     <t>Planning des salariés du 29/06/2026 au 05/07/2026</t>
   </si>
@@ -378,22 +378,7 @@
     <t>JPO PADEL KIDS // ANNIV</t>
   </si>
   <si>
-    <t>18:30/01:00+</t>
-  </si>
-  <si>
-    <t>18:00/19:00</t>
-  </si>
-  <si>
-    <t>EV-LO</t>
-  </si>
-  <si>
-    <t>19:00/23:00</t>
-  </si>
-  <si>
-    <t>23:00/00:30+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      C. PADEL    //    LEAGUES     //      16eme FRANCE</t>
+    <t>C. PADEL // LEAGUES</t>
   </si>
 </sst>
 </file>
@@ -782,7 +767,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -952,18 +937,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3620,138 +3593,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15BE6346-770A-4827-976C-2BE0919065FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="6867525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28838D5F-AC93-4BBB-B87B-CEC48C3B906C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="7248525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4796696F-9039-4729-AF11-3B924332FD4C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="7629525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4168,7 +4009,7 @@
         <v>114</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D3" s="56" t="s">
         <v>115</v>
@@ -4550,7 +4391,7 @@
       <c r="B26" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="21" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="49" t="s">
@@ -4570,8 +4411,8 @@
       <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="57" t="s">
-        <v>119</v>
+      <c r="C27" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>56</v>
@@ -4588,9 +4429,7 @@
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="28"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="59" t="s">
-        <v>120</v>
-      </c>
+      <c r="C28" s="1"/>
       <c r="D28" s="32" t="s">
         <v>54</v>
       </c>
@@ -4604,9 +4443,7 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
       <c r="B29" s="1"/>
-      <c r="C29" s="60" t="s">
-        <v>121</v>
-      </c>
+      <c r="C29" s="1"/>
       <c r="D29" s="31" t="s">
         <v>58</v>
       </c>
@@ -4620,9 +4457,7 @@
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="39" t="s">
-        <v>14</v>
-      </c>
+      <c r="C30" s="1"/>
       <c r="D30" s="52" t="s">
         <v>53</v>
       </c>
@@ -4634,9 +4469,7 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
       <c r="B31" s="1"/>
-      <c r="C31" s="57" t="s">
-        <v>122</v>
-      </c>
+      <c r="C31" s="1"/>
       <c r="D31" s="50" t="s">
         <v>60</v>
       </c>
@@ -4648,7 +4481,7 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="28"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="57"/>
+      <c r="C32" s="1"/>
       <c r="D32" s="2" t="s">
         <v>14</v>
       </c>
@@ -4660,7 +4493,7 @@
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23"/>
       <c r="B33" s="24"/>
-      <c r="C33" s="57"/>
+      <c r="C33" s="24"/>
       <c r="D33" s="24" t="s">
         <v>61</v>
       </c>
@@ -4748,8 +4581,8 @@
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23"/>
       <c r="B39" s="24"/>
-      <c r="C39" s="58" t="s">
-        <v>118</v>
+      <c r="C39" s="24" t="s">
+        <v>70</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24" t="s">
@@ -5916,13 +5749,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0E364D-2D39-4FA9-BB2A-721348C3EA28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A6ACA25-883F-46DD-8FAC-0088F0126280}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC0ACA86-0276-4A26-B4FA-4A2B4920F358}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69510268-CC1B-4632-A4CB-6AE030FC320A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8BB1F4E-294E-4892-B1AE-5BD18185F0D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCDBF4C9-CA0B-43D3-A1A0-B0B5BDEF8381}"/>
 </file>
--- a/Plannings 2026 S27.xlsx
+++ b/Plannings 2026 S27.xlsx
@@ -5916,13 +5916,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0E364D-2D39-4FA9-BB2A-721348C3EA28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3545BF3E-DE5B-4B56-B506-2F7A4E9E72F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC0ACA86-0276-4A26-B4FA-4A2B4920F358}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9F85C5D-0697-441E-A329-3E546D95320F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8BB1F4E-294E-4892-B1AE-5BD18185F0D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{870D485B-C52C-4117-A769-990B5BA3E185}"/>
 </file>